--- a/Anderson_Gallup_2015/Anderson_Gallup_2015_registry_rows.xlsx
+++ b/Anderson_Gallup_2015/Anderson_Gallup_2015_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R85f3eb54352c4d46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R2db1252b6cdd4afd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rb34e8569db3c4e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R8e12ee95dd1a487f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Rd51b228db7b04955"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rd69fc31426e942fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -350,13 +350,13 @@
         <x:v>Nicholas Saddler dissertation: Methods, Table 2 note and References (local final dissertation). Nick introduction/discussion and Anderson &amp; Gallup 2015 review.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Reference only — no independent dataset item selected</x:v>
+        <x:v>Reference only — Full text confirmed in EndNote, 10 pages. REFERENCE ONLY; no independent experimental dataset item assigned.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/0076593089/Anderson-2015-Mirror self-recognition_ a revie.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -525,11 +525,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Nick: cited in introduction/discussion; not named data source. Planned folder: Anderson_Gallup_2015. Target: Review evidence and cited primary studies; no dataset item assigned. SECONDARY context source, not new experimental observations. Use to trace primary studies and evaluate conditioning, controls and behavioural criteria. Do not double-count its summaries as extra data.
-Item check 2026-10-25: Reference only — no independent dataset item selected. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote correction 2026-10-25: Reference only — Full text confirmed in EndNote, 10 pages. REFERENCE ONLY; no independent experimental dataset item assigned. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/0076593089/Anderson-2015-Mirror self-recognition_ a revie.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>REFERENCE ONLY — methodological review</x:v>
@@ -713,7 +713,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>Blank Item number means full text is still required or the source is REFERENCE ONLY. The six EndNote PDFs identified on 2026-10-25 are linked in Source list and their source-folder notes. Smaers 2013 Table 1 is now verified. Human snapshot checks remain pending.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -997,13 +997,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F0E5514-F302-4AFB-A4CF-F286153C2D61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{294978EC-EC0B-4CA4-8228-9FF2DF466101}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{970F2321-8982-4473-BA0D-2AF38849D4BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DEE38D0-9080-484C-A648-1801BB9B5770}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44CD96DB-C280-4F0F-A173-B4D8C6D73D5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0592D5ED-D0A4-4D87-896B-C83309F96F60}"/>
 </file>